--- a/data/seed/portfolio/L-2025-4713/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-4713/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J151"/>
+  <dimension ref="A1:J145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -540,117 +540,117 @@
       <c r="B8" t="n">
         <v>100</v>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>7271000</v>
-      </c>
-      <c r="D8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n">
+        <v>55125000</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Namangan Farm Savdo AJ</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>274457134</t>
+          <t>235095589</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000568507538001</t>
+          <t>20208000843833461001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №60/26 от 01.07.2026, НДС 12%</t>
+          <t>Оплата по с/ф №6640 за поставленный товар</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>33929000</v>
+        <v>96325000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46206</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>11911000</v>
-      </c>
-      <c r="D9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n">
+        <v>19235000</v>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Yangi Hayot Yog' Zavodi MChJ</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>267931244</t>
+          <t>235095589</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000939314235001</t>
+          <t>20208000843833461001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №8232</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №7978 ОТ 03.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>22018000</v>
+        <v>115560000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>35567000</v>
+        <v>9184000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №2783</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5538</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>57585000</v>
+        <v>124744000</v>
       </c>
     </row>
     <row r="11">
@@ -662,35 +662,35 @@
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>7246000</v>
+        <v>48416000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Farovon Polimer AJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>246775255</t>
+          <t>218043266</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000612892647001</t>
+          <t>20208000906476650001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №700</t>
+          <t>Предоплата за товар по дог. №115/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>64831000</v>
+        <v>173160000</v>
       </c>
     </row>
     <row r="12">
@@ -702,35 +702,35 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>4563000</v>
+        <v>18862000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №222/26 от 06.07.2026</t>
+          <t>Предоплата за товар по дог. №235/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>69394000</v>
+        <v>192022000</v>
       </c>
     </row>
     <row r="13">
@@ -742,21 +742,21 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>3294000</v>
+        <v>4304000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ishonch Agro Servis MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>344975431</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000667171574001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -766,11 +766,11 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №231/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4613 06.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>72688000</v>
+        <v>196326000</v>
       </c>
     </row>
     <row r="14">
@@ -782,35 +782,35 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>3236000</v>
+        <v>3991000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>323776793</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000326719454001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1567</t>
+          <t>Оплата за товар по с/ф №296 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>75924000</v>
+        <v>200317000</v>
       </c>
     </row>
     <row r="15">
@@ -841,11 +841,11 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Перечисление заработной платы за июнь 2026 г. согласно реестру №113</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>61955000</v>
+        <v>186348000</v>
       </c>
     </row>
     <row r="16">
@@ -857,35 +857,35 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>7537000</v>
+        <v>4046000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4616 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по дог. №51/26, НДС 12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>69492000</v>
+        <v>190394000</v>
       </c>
     </row>
     <row r="17">
@@ -895,23 +895,23 @@
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>2290000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>3333000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Farg'ona Qurilish Materiallari MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>220015074</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000195676767001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -921,77 +921,77 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №5/24</t>
+          <t>Mahsulot uchun to'lov, shartnoma №207/26, QQS 12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>67202000</v>
+        <v>193727000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>3955000</v>
+        <v>2020000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Durdona Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>297543196</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000717157475001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №115/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №97/26, НДС 12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>71157000</v>
+        <v>195747000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46213</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>22385000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>30250000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Chirchiq Non MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>217661131</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000411109668001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1001,131 +1001,131 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №215/26 ОТ 10.07.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №112/26</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>93542000</v>
+        <v>165497000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>18605000</v>
+        <v>2290000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Urganch Qurilish MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>221933431</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000033309952001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №293/26</t>
+          <t>Арендная плата за июль 2026 г. по договору №40/22</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>74937000</v>
+        <v>163207000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46216</v>
+        <v>46212</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>61565000</v>
+        <v>2758000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №3433 ОТ 13.07.2026, В Т.Ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1312 ОТ 09.07.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>136502000</v>
+        <v>165965000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>3080000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>30873000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lazzat Logistik MChJ</t>
+          <t>Chirchiq Non MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>391180432</t>
+          <t>217661131</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000669064766001</t>
+          <t>20208000411109668001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №177/26 от 13.07.2026</t>
+          <t>Оплата за товары согласно с/ф №3228</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>139582000</v>
+        <v>135092000</v>
       </c>
     </row>
     <row r="23">
@@ -1135,37 +1135,37 @@
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>19136000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>6427000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Namangan Farm Savdo AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>274457134</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000568507538001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №289/26</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №222/26 ОТ 13.07.2026</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>120446000</v>
+        <v>141519000</v>
       </c>
     </row>
     <row r="24">
@@ -1176,76 +1176,76 @@
         <v>116</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>54382000</v>
+        <v>6190000</v>
       </c>
       <c r="D24" s="2" t="n"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Navro'z Agro Servis XK</t>
+          <t>Chust Sut XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>210181893</t>
+          <t>245713445</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000030618921001</t>
+          <t>20208000850753885001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №112/26, QQS bilan</t>
+          <t>Оплата за транспортные услуги по дог. №190/26</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>66064000</v>
+        <v>135329000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n">
-        <v>26899000</v>
-      </c>
+      <c r="C25" s="2" t="n">
+        <v>14127000</v>
+      </c>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>323776793</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000326719454001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Shartnoma №176/26 bo'yicha oldindan to'lov</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №369</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>92963000</v>
+        <v>121202000</v>
       </c>
     </row>
     <row r="26">
@@ -1255,37 +1255,37 @@
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>11595000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>1905000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №99/26, НДС 12%</t>
+          <t>Социальный налог за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>104558000</v>
+        <v>119297000</v>
       </c>
     </row>
     <row r="27">
@@ -1295,343 +1295,338 @@
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n">
-        <v>3901000</v>
-      </c>
+      <c r="C27" s="2" t="n">
+        <v>1905000</v>
+      </c>
+      <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №203/26 от 14.07.2026</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>108459000</v>
+        <v>117392000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>1905000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>2151000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Предоплата за товар по договору №187/26 от 15.07.2026</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>106554000</v>
+        <v>119543000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1905000</v>
+        <v>4128000</v>
       </c>
       <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Оплата за упаковочные материалы, с/ф №3260</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>104649000</v>
+        <v>115415000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>7595000</v>
+        <v>15964000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>235095589</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000843833461001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №206/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №8091 за поставленный товар</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>112244000</v>
+        <v>131379000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>7161000</v>
+        <v>6626000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Yangi Hayot Meva Eksport MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>246775255</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000612892647001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №199/26, НДС 12%</t>
+          <t>Оплата по с/ф №2552 за поставленный товар</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>119405000</v>
+        <v>138005000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n">
-        <v>10905000</v>
-      </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n">
+        <v>2646000</v>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Navro'z Agro Servis XK</t>
+          <t>Farovon Polimer AJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>210181893</t>
+          <t>218043266</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000030618921001</t>
+          <t>20208000906476650001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1290</t>
+          <t>Оплата за продукцию по договору №233/26, НДС 12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>108500000</v>
+        <v>140651000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n">
-        <v>8426000</v>
-      </c>
-      <c r="D33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n">
+        <v>5994000</v>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Yangi Hayot Yog' Zavodi MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>267931244</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000939314235001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9550</t>
+          <t>Предоплата за товар по договору №208/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>100074000</v>
+        <v>146645000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>72419000</v>
+        <v>12847000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Oltin Vodiy Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>323514708</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000325725800001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №261/26, QQS bilan</t>
+          <t>Оплата за сырье по дог. №100/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>27655000</v>
+        <v>133798000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>4843000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>16700000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>323776793</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4713)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000326719454001</t>
+          <t>16307000258034738417</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1641,11 +1636,11 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5394 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2025-4713 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>32498000</v>
+        <v>117098000</v>
       </c>
     </row>
     <row r="36">
@@ -1655,192 +1650,197 @@
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>8777000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>39542000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Lazzat Logistik MChJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>391180432</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000669064766001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №7656 за поставленный товар</t>
+          <t>Оплата за сырье по дог. №58/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>41275000</v>
+        <v>77556000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>16700000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>2206000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4713)</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>16307000258034738417</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-4713 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата по счет-фактуре №6786 за поставленный товар</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>24575000</v>
+        <v>79762000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>24885000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>14806000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Navro'z Agro Servis XK</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>210181893</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000030618921001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №6858</t>
+          <t>SHARTNOMA №208/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>-310000</v>
+        <v>94568000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n">
-        <v>4724000</v>
+        <v>7419000</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №294/26, НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №228/26, НДС 12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>4414000</v>
+        <v>101987000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n">
-        <v>3781000</v>
-      </c>
-      <c r="D40" s="2" t="n"/>
+      <c r="C40" s="2" t="n"/>
+      <c r="D40" s="2" t="n">
+        <v>5751000</v>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>НДС за июнь2026 г.</t>
+          <t>Предоплата за товар по договору №109/26 от 22.07.2026</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>633000</v>
+        <v>107738000</v>
       </c>
     </row>
     <row r="41">
@@ -1850,23 +1850,23 @@
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>6992000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>6762000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Oltin Vodiy Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>398597120</t>
+          <t>323514708</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000008215814001</t>
+          <t>20208000325725800001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1876,392 +1876,397 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №242/26 от 22.07.2026</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №129/26</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7625000</v>
+        <v>100976000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n">
-        <v>38792000</v>
-      </c>
+      <c r="C42" s="2" t="n">
+        <v>10562000</v>
+      </c>
+      <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lazzat Logistik MChJ</t>
+          <t>Oltin Vodiy Qog'oz MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>391180432</t>
+          <t>323514708</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000669064766001</t>
+          <t>20208000325725800001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1908 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №136/26</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>46417000</v>
+        <v>90414000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>11485000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>3718000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1475 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>57902000</v>
+        <v>86696000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>10131000</v>
+        <v>4483000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Farovon Polimer AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>218043266</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000906476650001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №166/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №2357 за поставленный товар</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>68033000</v>
+        <v>91179000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n">
-        <v>1431000</v>
-      </c>
-      <c r="D45" s="2" t="n"/>
+      <c r="C45" s="2" t="n"/>
+      <c r="D45" s="2" t="n">
+        <v>4123000</v>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000203972572001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №9631 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>66602000</v>
+        <v>95302000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46233</v>
+        <v>46227</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>19747000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>4783000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1321</t>
+          <t>Предоплата за материалы по дог. №112/26</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>86349000</v>
+        <v>90519000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n">
-        <v>53287000</v>
-      </c>
-      <c r="D47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n">
+        <v>33517000</v>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №10/26</t>
+          <t>Предоплата за товар по договору №269/26 от 27.07.2026</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>33062000</v>
+        <v>124036000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>2530000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Плата за SMS-информирование</t>
+          <t>Оплата по счет-фактуре №939 за поставленный товар</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32762000</v>
+        <v>126566000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>20212000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>1431000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000457036593001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №357 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>52974000</v>
+        <v>125135000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>9761000</v>
+        <v>7784000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Guliston Plastik MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>398597120</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000008215814001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №3215 ОТ 03.08.2026, В Т.Ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №5862 от 28.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>62735000</v>
+        <v>132919000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>3189000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>2935000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shahrisabz Avto Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>240541264</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000397339854001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2271,272 +2276,272 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №2/26</t>
+          <t>Оплата по с/ф №9816 за поставленный товар</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>59546000</v>
+        <v>135854000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>65788000</v>
+        <v>41117000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Navro'z Agro Servis XK</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>210181893</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000030618921001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №150/26</t>
+          <t>Оплата за транспортные услуги по договору №116/26</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>-6242000</v>
+        <v>94737000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n">
-        <v>15325000</v>
-      </c>
-      <c r="D53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n">
+        <v>6812000</v>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ish haqi, reestr №2596</t>
+          <t>SHARTNOMA №280/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>-21567000</v>
+        <v>101549000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46239</v>
+        <v>46232</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>5819000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>4208000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Guliston Mebel XK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>244594514</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000909023795001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №4013</t>
+          <t>Оплата за продукцию по договору №276/26, НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>-27386000</v>
+        <v>105757000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46240</v>
+        <v>46232</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>7488000</v>
+        <v>10863000</v>
       </c>
       <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Chust Sut XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>245713445</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000850753885001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №249/26</t>
+          <t>Предоплата за материалы по договору №210/26</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>-34874000</v>
+        <v>94894000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46240</v>
+        <v>46233</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>7697000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>2162000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №258/26</t>
+          <t>Оплата по счет-фактуре №7425 за поставленный товар</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>-42571000</v>
+        <v>97056000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46241</v>
+        <v>46233</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n"/>
-      <c r="D57" s="2" t="n">
-        <v>22810000</v>
-      </c>
+      <c r="C57" s="2" t="n">
+        <v>34824000</v>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Andijon Sut Mahsulotlari AJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>359712090</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000821581475001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №156/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №4673</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>-19761000</v>
+        <v>62232000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n"/>
-      <c r="D58" s="2" t="n">
-        <v>20271000</v>
-      </c>
+      <c r="C58" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>399616473</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2546,237 +2551,232 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Shartnoma №229/26 bo'yicha oldindan to'lov</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>510000</v>
+        <v>61932000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46241</v>
+        <v>46234</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n">
-        <v>10014000</v>
-      </c>
+      <c r="C59" s="2" t="n">
+        <v>32303000</v>
+      </c>
+      <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>382881934</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000054842421001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №245/26, QQS 12%</t>
+          <t>Предоплата за материалы по договору №59/26</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10524000</v>
+        <v>29629000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>11524000</v>
+        <v>19551000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №164/26 от 10.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9681 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>22048000</v>
+        <v>49180000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>2512000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>14586000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Farg'ona Qurilish Materiallari MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>220015074</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000195676767001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>АРЕНДНАЯ ПЛАТА ЗА АВГУСТ 2026 Г. О ДОГОВОРУ №5/24</t>
+          <t>Предоплата за товар по дог. №178/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>19536000</v>
+        <v>63766000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>9810000</v>
+        <v>22416000</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Samarqand Dori-Darmon MChJ</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>202193343</t>
+          <t>382881934</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000603330995001</t>
+          <t>20208000054842421001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №158/26</t>
+          <t>Оплата за транспортные услуги по договору №114/26</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9726000</v>
+        <v>41350000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>10321000</v>
+        <v>54740000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Samarqand Dori-Darmon MChJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>202193343</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000603330995001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №185/26</t>
+          <t>Оплата за сырье по договору №131/26 от 03.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>-595000</v>
+        <v>-13390000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>20133000</v>
+        <v>15325000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Namangan Farm Savdo AJ</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>274457134</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000568507538001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -2786,857 +2786,862 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4261</t>
+          <t>ЗАРАБОТНАЯ ПЛАТА ЗА ИЮЛЬ 2026 Г. (ПЕРЕЧИСЛЕНИЕ НА ПЛАСТИКОВЫЕ КАРТЫ)</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>-20728000</v>
+        <v>-28715000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46244</v>
+        <v>46238</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>21019000</v>
+        <v>53472000</v>
       </c>
       <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №164/26, QQS bilan</t>
+          <t>Оплата за упаковочные материалы, с/ф №8062</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>-41747000</v>
+        <v>-82187000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46245</v>
+        <v>46239</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>12546000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9219</t>
+          <t>Оплата за товар по с/ф №2874 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>-51747000</v>
+        <v>-69641000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46246</v>
+        <v>46239</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n"/>
       <c r="D67" s="2" t="n">
-        <v>3659000</v>
+        <v>8907000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>323776793</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000326719454001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №196/26 от 12.08.2026</t>
+          <t>Оплата за товар по счет-фактуре №2737 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>-48088000</v>
+        <v>-60734000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46248</v>
+        <v>46240</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
-      <c r="C68" s="2" t="n">
-        <v>2090000</v>
-      </c>
-      <c r="D68" s="2" t="n"/>
+      <c r="C68" s="2" t="n"/>
+      <c r="D68" s="2" t="n">
+        <v>4409000</v>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farovon Polimer AJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>218043266</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000906476650001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Оплата по счет-фактуре №1249 за поставленный товар</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>-50178000</v>
+        <v>-56325000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46248</v>
+        <v>46241</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>2090000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>21827000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Gulshan Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>249755718</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000702516982001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>Предоплата за товар по договору №244/26 от 07.08.2026</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>-52268000</v>
+        <v>-34498000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>35436000</v>
+        <v>48701000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Afrosiyob Trans Servis MChJ</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>280497557</t>
+          <t>235095589</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000837025169001</t>
+          <t>20208000843833461001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3689 за поставленный товар</t>
+          <t>Предоплата за товар по договору №240/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>-16832000</v>
+        <v>14203000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>31482000</v>
+        <v>7186000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Zafar Metall Servis XK</t>
+          <t>Durdona Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>271445945</t>
+          <t>297543196</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000419090237001</t>
+          <t>20208000717157475001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №7709 17.08.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun t'lov h/f №4928</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>14650000</v>
+        <v>21389000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>13265000</v>
+        <v>5214000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Ishonch Agro Servis MChJ</t>
+          <t>Durdona Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>344975431</t>
+          <t>297543196</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000667171574001</t>
+          <t>20208000717157475001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1015 за поставленный товар</t>
+          <t>Предоплата за товар по договору №28/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>27915000</v>
+        <v>26603000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>8081000</v>
+        <v>3498000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5535 за поставленный товар</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №6615 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>35996000</v>
+        <v>30101000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n"/>
       <c r="D74" s="2" t="n">
-        <v>5617000</v>
+        <v>3333000</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №108/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №2762 за поставленный товар</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>41613000</v>
+        <v>33434000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>13920000</v>
+        <v>2512000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Urganch Qurilish MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>221933431</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000033309952001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №10/26</t>
+          <t>Ijara haqi avgust oyi uchun, shartnoma №40/22</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>27693000</v>
+        <v>30922000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46253</v>
+        <v>46244</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>16306000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>17545000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>382881934</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000054842421001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1891</t>
+          <t>Оплата за сырье по договору №133/26 от 10.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>43999000</v>
+        <v>13377000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>18128000</v>
+        <v>29949000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Lazzat Logistik MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>391180432</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000669064766001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3895 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №53</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>62127000</v>
+        <v>43326000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46254</v>
+        <v>46245</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>16700000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>5160000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4713)</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>16307000258034738417</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-4713 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за товар по дог. №147/26 от 11.08.2026</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>45427000</v>
+        <v>48486000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46258</v>
+        <v>46246</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>16054000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>47941000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Mehnat Logistik XK</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>240176611</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000144111096001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №170/26, НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №3401</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>61481000</v>
+        <v>545000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46258</v>
+        <v>46247</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>14640000</v>
+        <v>20249000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №785 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товар по с/ф №8592 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>76121000</v>
+        <v>20794000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46258</v>
+        <v>46247</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>14570000</v>
+        <v>2813000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Gulshan Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>249755718</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000702516982001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №601 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №1399 за поставленный товар</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>90691000</v>
+        <v>23607000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>9436000</v>
+        <v>8588000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ishonch Agro Servis MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>344975431</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000667171574001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1531 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №1145 за поставленный товар</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>100127000</v>
+        <v>32195000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>6729000</v>
+        <v>5149000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №13/26 от 24.08.2026</t>
+          <t>Shartnoma №149/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>106856000</v>
+        <v>37344000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>3394000</v>
+        <v>2919000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5788 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №246/26, QQS 12%</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>110250000</v>
+        <v>40263000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>1570000</v>
+        <v>2090000</v>
       </c>
       <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000203972572001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Социальный налог за июль 2026 г.</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>108680000</v>
+        <v>38173000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>4272000</v>
+        <v>2090000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
@@ -3661,237 +3666,232 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>НДС за июль 2026 г.</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>104408000</v>
+        <v>36083000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46258</v>
+        <v>46251</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>15899000</v>
+        <v>26948000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №2279</t>
+          <t>Предоплата за материалы по дог. №56/26</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>88509000</v>
+        <v>9135000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46259</v>
+        <v>46252</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>7912000</v>
+        <v>3165000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №80/26 от 25.08.2026</t>
+          <t>Предоплата за товар по договору №290/26 от 18.08.2026</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>96421000</v>
+        <v>12300000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46259</v>
+        <v>46253</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
       <c r="C89" s="2" t="n"/>
       <c r="D89" s="2" t="n">
-        <v>6844000</v>
+        <v>32830000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1617 от 25.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по с/ф №4166 за поставленный товар</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>103265000</v>
+        <v>45130000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46259</v>
+        <v>46253</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>19452000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>24118000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №202/26</t>
+          <t>Оплата за товар по с/ф №7429 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>83813000</v>
+        <v>69248000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46260</v>
+        <v>46254</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>4849000</v>
+        <v>6874000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>323776793</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000326719454001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №61/26, НДС 12%</t>
+          <t>Предоплата за товар по договору №275/26 от 20.08.2026</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>88662000</v>
+        <v>76122000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46261</v>
+        <v>46254</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>37168000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>16700000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>399616473</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4713)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>16307000258034738417</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3901,606 +3901,606 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Shartnoma №205/26 bo'yicha oldindan to'lov</t>
+          <t>Kredit shartnomasi L-2025-4713 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>125830000</v>
+        <v>59422000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46261</v>
+        <v>46255</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>4817000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>5875000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Navro'z Agro Servis XK</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>210181893</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000030618921001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №2853</t>
+          <t>Shartnoma №191/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>121013000</v>
+        <v>65297000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46261</v>
+        <v>46255</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>24914000</v>
+        <v>33194000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Samarqand Dori-Darmon MChJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>202193343</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000603330995001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №89/26</t>
+          <t>Оплата за транспортные услуги по дог. №197/26</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>96099000</v>
+        <v>32103000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n"/>
       <c r="D95" s="2" t="n">
-        <v>7836000</v>
+        <v>5214000</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №297/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №94/26, НДС 12%</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>103935000</v>
+        <v>37317000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>300000</v>
+        <v>1570000</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000457036593001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>103635000</v>
+        <v>35747000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>6010000</v>
+        <v>4263000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №271/26 от 31.08.2026, НДС 12%</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>97625000</v>
+        <v>31484000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46265</v>
+        <v>46258</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>6050000</v>
+        <v>18775000</v>
       </c>
       <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4266</t>
+          <t>Tovarlar uchun to'lov h/f №9292</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>91575000</v>
+        <v>12709000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46265</v>
+        <v>46259</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>12796000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>7458000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №134/26</t>
+          <t>Оплата за продукцию по договору №83/26, НДС 12%</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>78779000</v>
+        <v>20167000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46265</v>
+        <v>46260</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>30209000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>8037000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №227/26 от 31.08.2026, НДС 12%</t>
+          <t>Оплата за товар по с/ф №3664 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>48570000</v>
+        <v>28204000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46266</v>
+        <v>46260</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>20023000</v>
+        <v>6189000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>323776793</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000326719454001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №21/26 от 01.09.2026</t>
+          <t>Оплата по с/ф №3207 за поставленный товар</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>68593000</v>
+        <v>34393000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46266</v>
+        <v>46261</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n">
-        <v>15919000</v>
-      </c>
-      <c r="D102" s="2" t="n"/>
+      <c r="C102" s="2" t="n"/>
+      <c r="D102" s="2" t="n">
+        <v>18035000</v>
+      </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Yangi Hayot Yog' Zavodi MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>267931244</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000939314235001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №283/26</t>
+          <t>Предоплата за товар по договору №88/26 от 27.08.2026</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>52674000</v>
+        <v>52428000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46267</v>
+        <v>46261</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>5776000</v>
+        <v>5228000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №26/26 от 02.09.2026</t>
+          <t>Оплата за товар по с/ф №2133 от 27.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>58450000</v>
+        <v>57656000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46268</v>
+        <v>46262</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>6886000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>18142000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Afrosiyob Trans Servis MChJ</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>280497557</t>
+          <t>382881934</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000837025169001</t>
+          <t>20208000054842421001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №112/26 от 03.09.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №238/26, QQS bilan</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>65336000</v>
+        <v>39514000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>5345000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>7630000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Yangi Hayot Yog' Zavodi MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>267931244</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000939314235001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №124/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9850</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>59991000</v>
+        <v>47144000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46272</v>
+        <v>46265</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n"/>
-      <c r="D106" s="2" t="n">
-        <v>36903000</v>
-      </c>
+      <c r="C106" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zafar Metall Servis XK</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>271445945</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000419090237001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №70/26, НДС 12%</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>96894000</v>
+        <v>46844000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46272</v>
+        <v>46269</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>35062000</v>
+        <v>14918000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>323776793</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000326719454001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3117 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №6095 за поставленный товар</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>131956000</v>
+        <v>61762000</v>
       </c>
     </row>
     <row r="108">
@@ -4512,35 +4512,35 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>21299000</v>
+        <v>36070000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2987 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №109/26, НДС 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>153255000</v>
+        <v>97832000</v>
       </c>
     </row>
     <row r="109">
@@ -4550,32 +4550,37 @@
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>15008000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>5606000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zarafshon Kredit Bank</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №209/26, НДС 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>138247000</v>
+        <v>103438000</v>
       </c>
     </row>
     <row r="110">
@@ -4586,142 +4591,137 @@
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>30071000</v>
+        <v>12271000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Chust Sut XK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>245713445</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000850753885001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №36/26</t>
+          <t>Оплата за транспортные услуги по договору №105/26</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>108176000</v>
+        <v>91167000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>2460000</v>
+        <v>15008000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Farg'ona Qurilish Materiallari MChJ</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>220015074</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000195676767001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №1555</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>105716000</v>
+        <v>76159000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n">
-        <v>6958000</v>
-      </c>
+      <c r="C112" s="2" t="n">
+        <v>15558000</v>
+      </c>
+      <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3720 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по дог. №204/26</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>112674000</v>
+        <v>60601000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46274</v>
+        <v>46272</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>97296000</v>
+        <v>27498000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Chirchiq Non MChJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>217661131</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000411109668001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -4731,197 +4731,197 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №944</t>
+          <t>Предоплата за материалы по договору №293/26</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>15378000</v>
+        <v>33103000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>4590000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>51320000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8964 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №292/26, QQS bilan</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>19968000</v>
+        <v>-18217000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>20560000</v>
+        <v>16680000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4864 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №519 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>40528000</v>
+        <v>-1537000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>18183000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>4132000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Navro'z Agro Servis XK</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>210181893</t>
+          <t>235095589</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000030618921001</t>
+          <t>20208000843833461001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №164/26</t>
+          <t>Оплата по счет-фактуре №6067 за поставленный товар</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>22345000</v>
+        <v>2595000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>9711000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>2460000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Urganch Qurilish MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>221933431</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000033309952001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Shartnoma №28/26 bo'yicha oldindan to'lov</t>
+          <t>АРЕНДНАЯ ПЛАТА ЗА СЕНТЯБРЬ 2026 Г. ПО ДОГОВОРУ №40/22</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>32056000</v>
+        <v>135000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>7154000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>14502000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Chirchiq Non MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>217661131</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000411109668001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4931,37 +4931,37 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5243 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №69/26</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>39210000</v>
+        <v>-14367000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>4779000</v>
+        <v>75849000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Ishonch Agro Servis MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>344975431</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000667171574001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -4971,392 +4971,392 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1177 14.09.2026, QQS bilan</t>
+          <t>Оплата за товар по с/ф №1331 от 11.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>43989000</v>
+        <v>61482000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>5575000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>21271000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №134/26, QQS bilan</t>
+          <t>Предоплата за товар по дог. №125/26 от 11.09.2026</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>38414000</v>
+        <v>82753000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46279</v>
+        <v>46276</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>13972000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>14451000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Navro'z Agro Servis XK</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>210181893</t>
+          <t>235095589</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000030618921001</t>
+          <t>20208000843833461001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №93/26 от 14.09.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №50/26, НДС 12%</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>24442000</v>
+        <v>97204000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>8552000</v>
+        <v>27578000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2029 15.09.2026, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №946 от 14.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>32994000</v>
+        <v>124782000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>2047000</v>
+        <v>11726000</v>
       </c>
       <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Оплата за сырье по договору №179/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>30947000</v>
+        <v>113056000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>2047000</v>
+        <v>122079000</v>
       </c>
       <c r="D124" s="2" t="n"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chust Sut XK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>245713445</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000850753885001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Оплата за сырье по договору №278/26 от 14.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>28900000</v>
+        <v>-9023000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>14321000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>2047000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №36/26 от 17.09.2026</t>
+          <t>Социальный налог за август 2026 г.</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>43221000</v>
+        <v>-11070000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46283</v>
+        <v>46281</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>10429000</v>
+        <v>2047000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №279/26 от 18.09.2026, НДС 12%</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>32792000</v>
+        <v>-13117000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>16700000</v>
+        <v>31740000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-4713)</t>
+          <t>Qarshi Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>382881934</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>16307000258034738417</t>
+          <t>20208000054842421001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-4713 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за товары согласно счет-фактуре №8010</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>16092000</v>
+        <v>-44857000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>31756000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>7305000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Qarshi Polimer MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>382881934</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000054842421001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1015 21.09.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №142/26</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>47848000</v>
+        <v>-52162000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46286</v>
+        <v>46285</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>30088000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>16700000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>399616473</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-4713)</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>16307000258034738417</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5366,11 +5366,11 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №700 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-4713 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>77936000</v>
+        <v>-68862000</v>
       </c>
     </row>
     <row r="130">
@@ -5382,35 +5382,35 @@
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>18103000</v>
+        <v>20533000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2786</t>
+          <t>Оплата за продукцию по договору №19/26, НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>96039000</v>
+        <v>-48329000</v>
       </c>
     </row>
     <row r="131">
@@ -5422,341 +5422,341 @@
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>6192000</v>
+        <v>6184000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Qo'qon Logistik MChJ</t>
+          <t>Zafar Yog'och MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>323776793</t>
+          <t>277679343</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000326719454001</t>
+          <t>20208000671945475001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9313 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №2479 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>102231000</v>
+        <v>-42145000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n"/>
       <c r="D132" s="2" t="n">
-        <v>5117000</v>
+        <v>8541000</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8666 21.09.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №189/26, НДС 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>107348000</v>
+        <v>-33604000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n">
-        <v>4042000</v>
-      </c>
-      <c r="D133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n">
+        <v>6877000</v>
+      </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Оплата по счет-фактуре №1307 за поставленный товар</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>103306000</v>
+        <v>-26727000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>6064000</v>
+        <v>4036000</v>
       </c>
       <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №30/26</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>97242000</v>
+        <v>-30763000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>8436000</v>
+        <v>7117000</v>
       </c>
       <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Navro'z Agro Servis XK</t>
+          <t>Durdona Savdo MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>210181893</t>
+          <t>377525556</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000030618921001</t>
+          <t>20208000289264771001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №143/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №145/26</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>88806000</v>
+        <v>-37880000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>13212000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>12175000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №171/26</t>
+          <t>Оплата за товар по с/ф №6351 от 23.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>75594000</v>
+        <v>-25705000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>16518000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>4584000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>235095589</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000843833461001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №1751</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №7289 ОТ 24.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>59076000</v>
+        <v>-21121000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>17897000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>18079000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Yangi Hayot Yog' Zavodi MChJ</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>267931244</t>
+          <t>235095589</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000939314235001</t>
+          <t>20208000843833461001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №292/26</t>
+          <t>Предоплата за товар по договору №278/26 от 28.09.2026</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>41179000</v>
+        <v>-3042000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
       <c r="C139" s="2" t="n"/>
       <c r="D139" s="2" t="n">
-        <v>14470000</v>
+        <v>6949000</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Lazzat Logistik MChJ</t>
+          <t>Ziyo Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>391180432</t>
+          <t>235095589</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000669064766001</t>
+          <t>20208000843833461001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5766,157 +5766,152 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №291/26 от 23.09.2026</t>
+          <t>Оплата за товар по с/ф №7021 от 28.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>55649000</v>
+        <v>3907000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n">
-        <v>8466000</v>
-      </c>
-      <c r="D140" s="2" t="n"/>
+      <c r="C140" s="2" t="n"/>
+      <c r="D140" s="2" t="n">
+        <v>4115000</v>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
+          <t>Gulshan Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>273091776</t>
+          <t>249755718</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>20208000702516982001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №3163</t>
+          <t>Оплата по счет-фактуре №513 за поставленный товар</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>47183000</v>
+        <v>8022000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46289</v>
+        <v>46293</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>12191000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>1537000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Namangan Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>399616473</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000496661362001</t>
+          <t>20208000457036593001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8561 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>59374000</v>
+        <v>6485000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
-      <c r="C142" s="2" t="n">
-        <v>5770000</v>
-      </c>
-      <c r="D142" s="2" t="n"/>
+      <c r="C142" s="2" t="n"/>
+      <c r="D142" s="2" t="n">
+        <v>31715000</v>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Namangan Farm Savdo AJ</t>
+          <t>Afrosiyob Oziq-ovqat Savdo AJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>274457134</t>
+          <t>361647334</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000568507538001</t>
+          <t>20208000666136268001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №228/26</t>
+          <t>Оплата за товар по счет-фактуре №7894 от 29.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>53604000</v>
+        <v>38200000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>12929000</v>
+        <v>300000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lazzat Trans Servis AJ</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>273091776</t>
+          <t>Zarafshon Kredit Bank</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000463250427001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -5926,271 +5921,36 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №184/26</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>40675000</v>
+        <v>37900000</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B144" t="n">
-        <v>236</v>
-      </c>
-      <c r="C144" s="2" t="n"/>
-      <c r="D144" s="2" t="n">
-        <v>5286000</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Namangan Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>399616473</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>20208000496661362001</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №9563 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J144" s="2" t="n">
-        <v>45961000</v>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="n">
+        <v>1004663000</v>
+      </c>
+      <c r="D144" s="4" t="n">
+        <v>1001363000</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B145" t="n">
-        <v>237</v>
-      </c>
-      <c r="C145" s="2" t="n">
-        <v>1537000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>20208000203972572001</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I145" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
-        </is>
-      </c>
-      <c r="J145" s="2" t="n">
-        <v>44424000</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B146" t="n">
-        <v>238</v>
-      </c>
-      <c r="C146" s="2" t="n">
-        <v>8745000</v>
-      </c>
-      <c r="D146" s="2" t="n"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Lazzat Trans Servis AJ</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>273091776</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>20208000463250427001</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr">
-        <is>
-          <t>Предоплата за материалы по договору №154/26</t>
-        </is>
-      </c>
-      <c r="J146" s="2" t="n">
-        <v>35679000</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B147" t="n">
-        <v>239</v>
-      </c>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n">
-        <v>11021000</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Namangan Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>399616473</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>20208000496661362001</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №9301 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J147" s="2" t="n">
-        <v>46700000</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B148" t="n">
-        <v>240</v>
-      </c>
-      <c r="C148" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D148" s="2" t="n"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Zarafshon Kredit Bank</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>Плата за SMS-информирование</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="n">
-        <v>46400000</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B149" t="n">
-        <v>241</v>
-      </c>
-      <c r="C149" s="2" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Lazzat Trans Servis AJ</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>273091776</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>20208000463250427001</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №69/26 от 30.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J149" s="2" t="n">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="n">
         <v>37900000</v>
       </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C150" s="4" t="n">
-        <v>1011166000</v>
-      </c>
-      <c r="D150" s="4" t="n">
-        <v>1007866000</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C151" s="4" t="n">
-        <v>37900000</v>
-      </c>
-      <c r="D151" s="4" t="n"/>
+      <c r="D145" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
